--- a/downloads/doujin_uriage_kanri_v1_1.xlsx
+++ b/downloads/doujin_uriage_kanri_v1_1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\81808\Desktop\New\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B84B4114-E69A-44AB-A39A-29C2115F1963}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E26655E4-2D44-46A4-9EAB-16917EE25E75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -252,7 +252,7 @@
     <t>2026-04-26</t>
   </si>
   <si>
-    <t>2025/10/28改定: 5.6%+45円(Sheet1の式は別途BOOTH固定式)</t>
+    <t>2025/10/28改定: 5.6%+45円・1件ごと小数点切り上げ(Sheet1の式は別途 ROUNDUP 固定式)</t>
   </si>
   <si>
     <t>▼ Sheet 1 から月次の手取りを自動集計します。サンプル数値が入っていますが、本番運用では Sheet 1 を埋めると自動更新されます。</t>
@@ -1061,7 +1061,7 @@
         <v>88000</v>
       </c>
       <c r="K7" s="2">
-        <f t="shared" ref="K7:K12" si="0">IF(D7="BOOTH",MAX(0,E7*0.944-45),IF(D7="DLsite",IF(F7="併売",E7*0.55,IF(F7="専売",IF(E7&lt;500,E7*0.5,IF(E7&lt;1100,E7*0.6,IF(E7&lt;2200,E7*0.65,IF(E7&lt;4400,E7*0.7,E7*0.75)))),0)),IF(D7="FANZA同人",IF(E7&lt;550,E7*0.55,IF(E7&lt;1100,E7*0.6,IF(E7&lt;4400,E7*0.65,E7*0.8))),0)))</f>
+        <f t="shared" ref="K7:K12" si="0">IF(D7="BOOTH",MAX(0,E7-ROUNDUP(E7*0.056+45,0)),IF(D7="DLsite",IF(F7="併売",E7*0.55,IF(F7="専売",IF(E7&lt;500,E7*0.5,IF(E7&lt;1100,E7*0.6,IF(E7&lt;2200,E7*0.65,IF(E7&lt;4400,E7*0.7,E7*0.75)))),0)),IF(D7="FANZA同人",IF(E7&lt;550,E7*0.55,IF(E7&lt;1100,E7*0.6,IF(E7&lt;4400,E7*0.65,E7*0.8))),0)))</f>
         <v>715</v>
       </c>
       <c r="L7" s="2">
@@ -1158,15 +1158,15 @@
       </c>
       <c r="K9" s="2">
         <f t="shared" si="0"/>
-        <v>993.39999999999986</v>
+        <v>993</v>
       </c>
       <c r="L9" s="2">
         <f t="shared" si="1"/>
-        <v>99339.999999999985</v>
+        <v>99300</v>
       </c>
       <c r="M9" s="2">
         <f t="shared" si="2"/>
-        <v>0.90309090909090894</v>
+        <v>0.90272727272727271</v>
       </c>
       <c r="N9" t="s">
         <v>27</v>
@@ -1286,11 +1286,11 @@
       </c>
       <c r="L13" s="3">
         <f>SUM(L7:L12)</f>
-        <v>290740</v>
+        <v>290700</v>
       </c>
       <c r="M13">
         <f t="shared" si="2"/>
-        <v>0.73419191919191917</v>
+        <v>0.73409090909090913</v>
       </c>
     </row>
   </sheetData>
@@ -2031,15 +2031,15 @@
       </c>
       <c r="D7">
         <f>SUMIFS('1_作品別売上'!L:L,'1_作品別売上'!D:D,"BOOTH",'1_作品別売上'!H:H,"&gt;="&amp;DATE(2026,1,1),'1_作品別売上'!H:H,"&lt;"&amp;DATE(2026,2,1))</f>
-        <v>99339.999999999985</v>
+        <v>99300</v>
       </c>
       <c r="E7">
         <f t="shared" ref="E7:E18" si="0">SUM(B7:D7)</f>
-        <v>177990</v>
+        <v>177950</v>
       </c>
       <c r="G7">
         <f>SUM(E$7:E7)</f>
-        <v>177990</v>
+        <v>177950</v>
       </c>
       <c r="H7">
         <f>SUMIFS('1_作品別売上'!J:J,'1_作品別売上'!H:H,"&gt;="&amp;DATE(2026,1,1),'1_作品別売上'!H:H,"&lt;"&amp;DATE(2026,2,1))</f>
@@ -2072,11 +2072,11 @@
       </c>
       <c r="F8">
         <f t="shared" ref="F8:F18" si="1">IF(E7=0,"",E8/E7-1)</f>
-        <v>-0.36653744592392834</v>
+        <v>-0.36639505479067158</v>
       </c>
       <c r="G8">
         <f>SUM(E$7:E8)</f>
-        <v>290740</v>
+        <v>290700</v>
       </c>
       <c r="H8">
         <f>SUMIFS('1_作品別売上'!J:J,'1_作品別売上'!H:H,"&gt;="&amp;DATE(2026,2,1),'1_作品別売上'!H:H,"&lt;"&amp;DATE(2026,3,1))</f>
@@ -2113,7 +2113,7 @@
       </c>
       <c r="G9">
         <f>SUM(E$7:E9)</f>
-        <v>290740</v>
+        <v>290700</v>
       </c>
       <c r="H9">
         <f>SUMIFS('1_作品別売上'!J:J,'1_作品別売上'!H:H,"&gt;="&amp;DATE(2026,3,1),'1_作品別売上'!H:H,"&lt;"&amp;DATE(2026,4,1))</f>
@@ -2150,7 +2150,7 @@
       </c>
       <c r="G10">
         <f>SUM(E$7:E10)</f>
-        <v>290740</v>
+        <v>290700</v>
       </c>
       <c r="H10">
         <f>SUMIFS('1_作品別売上'!J:J,'1_作品別売上'!H:H,"&gt;="&amp;DATE(2026,4,1),'1_作品別売上'!H:H,"&lt;"&amp;DATE(2026,5,1))</f>
@@ -2187,7 +2187,7 @@
       </c>
       <c r="G11">
         <f>SUM(E$7:E11)</f>
-        <v>290740</v>
+        <v>290700</v>
       </c>
       <c r="H11">
         <f>SUMIFS('1_作品別売上'!J:J,'1_作品別売上'!H:H,"&gt;="&amp;DATE(2026,5,1),'1_作品別売上'!H:H,"&lt;"&amp;DATE(2026,6,1))</f>
@@ -2224,7 +2224,7 @@
       </c>
       <c r="G12">
         <f>SUM(E$7:E12)</f>
-        <v>290740</v>
+        <v>290700</v>
       </c>
       <c r="H12">
         <f>SUMIFS('1_作品別売上'!J:J,'1_作品別売上'!H:H,"&gt;="&amp;DATE(2026,6,1),'1_作品別売上'!H:H,"&lt;"&amp;DATE(2026,7,1))</f>
@@ -2261,7 +2261,7 @@
       </c>
       <c r="G13">
         <f>SUM(E$7:E13)</f>
-        <v>290740</v>
+        <v>290700</v>
       </c>
       <c r="H13">
         <f>SUMIFS('1_作品別売上'!J:J,'1_作品別売上'!H:H,"&gt;="&amp;DATE(2026,7,1),'1_作品別売上'!H:H,"&lt;"&amp;DATE(2026,8,1))</f>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="G14">
         <f>SUM(E$7:E14)</f>
-        <v>290740</v>
+        <v>290700</v>
       </c>
       <c r="H14">
         <f>SUMIFS('1_作品別売上'!J:J,'1_作品別売上'!H:H,"&gt;="&amp;DATE(2026,8,1),'1_作品別売上'!H:H,"&lt;"&amp;DATE(2026,9,1))</f>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="G15">
         <f>SUM(E$7:E15)</f>
-        <v>290740</v>
+        <v>290700</v>
       </c>
       <c r="H15">
         <f>SUMIFS('1_作品別売上'!J:J,'1_作品別売上'!H:H,"&gt;="&amp;DATE(2026,9,1),'1_作品別売上'!H:H,"&lt;"&amp;DATE(2026,10,1))</f>
@@ -2372,7 +2372,7 @@
       </c>
       <c r="G16">
         <f>SUM(E$7:E16)</f>
-        <v>290740</v>
+        <v>290700</v>
       </c>
       <c r="H16">
         <f>SUMIFS('1_作品別売上'!J:J,'1_作品別売上'!H:H,"&gt;="&amp;DATE(2026,10,1),'1_作品別売上'!H:H,"&lt;"&amp;DATE(2026,11,1))</f>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="G17">
         <f>SUM(E$7:E17)</f>
-        <v>290740</v>
+        <v>290700</v>
       </c>
       <c r="H17">
         <f>SUMIFS('1_作品別売上'!J:J,'1_作品別売上'!H:H,"&gt;="&amp;DATE(2026,11,1),'1_作品別売上'!H:H,"&lt;"&amp;DATE(2026,12,1))</f>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="G18">
         <f>SUM(E$7:E18)</f>
-        <v>290740</v>
+        <v>290700</v>
       </c>
       <c r="H18">
         <f>SUMIFS('1_作品別売上'!J:J,'1_作品別売上'!H:H,"&gt;="&amp;DATE(2026,12,1),'1_作品別売上'!H:H,"&lt;"&amp;DATE(2027,1,1))</f>
@@ -2933,7 +2933,7 @@
       </c>
       <c r="B8">
         <f>SUM('3_月次集計'!E7:E18)</f>
-        <v>290740</v>
+        <v>290700</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.15">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="B10">
         <f>B8-B9</f>
-        <v>254140</v>
+        <v>254100</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.15">
